--- a/tame_output/ON/bt/strategyON_20230902.xlsx
+++ b/tame_output/ON/bt/strategyON_20230902.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,12 +623,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -661,12 +661,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.7%</t>
+          <t>-19.6%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,16 +758,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>4.5%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.6%</t>
+          <t>454.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-20.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>101.4%</t>
+          <t>101.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>97.2%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1222,11 +1222,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1278,12 +1278,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1360,26 +1360,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.3%</t>
+          <t>132.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>126.8%</t>
+          <t>127.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>9.0%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1707"/>
+  <dimension ref="A1:G1708"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40771,7 +40771,7 @@
         <v>45169</v>
       </c>
       <c r="B1707" t="n">
-        <v>2.770405762234912</v>
+        <v>2.771726246868203</v>
       </c>
       <c r="C1707" t="n">
         <v>2.891093788499763</v>
@@ -40787,6 +40787,29 @@
       </c>
       <c r="G1707" t="n">
         <v>4.191539664879173</v>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B1708" t="n">
+        <v>2.759739359862337</v>
+      </c>
+      <c r="C1708" t="n">
+        <v>2.900444369465165</v>
+      </c>
+      <c r="D1708" t="n">
+        <v>1.559426950055598</v>
+      </c>
+      <c r="E1708" t="n">
+        <v>3.523858725173658</v>
+      </c>
+      <c r="F1708" t="n">
+        <v>2.167535300960072</v>
+      </c>
+      <c r="G1708" t="n">
+        <v>4.20096555004121</v>
       </c>
     </row>
   </sheetData>
